--- a/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-17 - 2026-08-23).xlsx
+++ b/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-17 - 2026-08-23).xlsx
@@ -207,33 +207,33 @@
 21</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>R$ 1.026.179,97</t>
-  </si>
-  <si>
-    <t>R$ 52.432,55
-R$ 48.865,71</t>
-  </si>
-  <si>
-    <t>7.1%
-10.3%</t>
-  </si>
-  <si>
-    <t>559.6</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>30.8%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>R$ 1.152.797,70</t>
+  </si>
+  <si>
+    <t>R$ 55.271,12
+R$ 54.895,13</t>
+  </si>
+  <si>
+    <t>12.9%
+10.9%</t>
+  </si>
+  <si>
+    <t>586.3</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>30.9%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -242,28 +242,28 @@
     <t>23.2</t>
   </si>
   <si>
-    <t>81.5%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>3.7</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>16.1</t>
-  </si>
-  <si>
-    <t>86.3%</t>
-  </si>
-  <si>
-    <t>-R$ 11.356,38</t>
+    <t>82.8%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>86.2%</t>
+  </si>
+  <si>
+    <t>-R$ 12.363,58</t>
   </si>
   <si>
     <t>4.68</t>
@@ -872,7 +872,7 @@
         <v>19504</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="s" r="C2" s="4">
         <v>44</v>
@@ -909,59 +909,59 @@
         <v>52</v>
       </c>
       <c r="O2" s="5">
-        <v>21315.169999999998</v>
+        <v>61115.299999999996</v>
       </c>
       <c r="P2" s="5">
-        <v>37301.547500000001</v>
+        <v>61115.299999999996</v>
       </c>
       <c r="Q2" s="6">
-        <v>-0.44464514222375418</v>
+        <v>-0.090099982059655859</v>
       </c>
       <c r="R2" s="7">
-        <v>376.25</v>
+        <v>570</v>
       </c>
       <c r="S2" s="6">
-        <v>-0.30420711974110037</v>
+        <v>-0.21595598349381018</v>
       </c>
       <c r="T2" s="6">
-        <v>0.366937143827612</v>
+        <v>0.31692004948024471</v>
       </c>
       <c r="U2" s="6">
-        <v>0.042441022051430979</v>
+        <v>0.016535039507291953</v>
       </c>
       <c r="V2" s="6">
-        <v>0.020124751526729556</v>
+        <v>0.014389326404353737</v>
       </c>
       <c r="W2" s="6">
-        <v>-0.017057217934457008</v>
+        <v>-0.010954900000490875</v>
       </c>
       <c r="X2" s="8">
-        <v>19.505339062499999</v>
+        <v>19.301255324675324</v>
       </c>
       <c r="Y2" s="6">
-        <v>0.96875</v>
+        <v>0.92727272727272725</v>
       </c>
       <c r="Z2" s="6">
-        <v>0.0078125</v>
+        <v>0.0025974025974025974</v>
       </c>
       <c r="AA2" s="8">
-        <v>3.981633980582524</v>
+        <v>3.9917560931899638</v>
       </c>
       <c r="AB2" s="8">
-        <v>2.7429679687499999</v>
+        <v>3.0813418181818184</v>
       </c>
       <c r="AC2" s="8">
-        <v>6.9693240000000003</v>
+        <v>7.2980939999999999</v>
       </c>
       <c r="AD2" s="8">
-        <v>13.86171875</v>
+        <v>14.233722857142856</v>
       </c>
       <c r="AE2" s="6">
-        <v>0.984375</v>
+        <v>0.98441558441558441</v>
       </c>
       <c r="AF2" s="9"/>
       <c r="AG2" s="5">
-        <v>-274.60000000000002</v>
+        <v>-548.29999999999995</v>
       </c>
       <c r="AH2" s="10">
         <v>5</v>
@@ -1134,7 +1134,7 @@
         <v>19507</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C4" s="4">
         <v>44</v>
@@ -1171,59 +1171,59 @@
         <v>52</v>
       </c>
       <c r="O4" s="5">
-        <v>21789.949999999997</v>
+        <v>74836.419999999998</v>
       </c>
       <c r="P4" s="5">
-        <v>50843.216666666653</v>
+        <v>74836.419999999998</v>
       </c>
       <c r="Q4" s="6">
-        <v>-0.23438552985833028</v>
+        <v>0.12691229630959211</v>
       </c>
       <c r="R4" s="7">
-        <v>534.33333333333326</v>
+        <v>761</v>
       </c>
       <c r="S4" s="6">
-        <v>0.01777777777777767</v>
+        <v>0.018741633199464536</v>
       </c>
       <c r="T4" s="6">
-        <v>0.32026949121039744</v>
+        <v>0.311253298861704</v>
       </c>
       <c r="U4" s="6">
-        <v>-0.0086743567562110047</v>
+        <v>0.00073403564734924524</v>
       </c>
       <c r="V4" s="6">
-        <v>0.031089272806959174</v>
+        <v>0.02503506447796407</v>
       </c>
       <c r="W4" s="6">
-        <v>-0.00060974440051491633</v>
+        <v>-0.0013643811395574509</v>
       </c>
       <c r="X4" s="8">
-        <v>21.195664739884393</v>
+        <v>23.724302051282052</v>
       </c>
       <c r="Y4" s="6">
-        <v>0.98843930635838151</v>
+        <v>0.97264957264957264</v>
       </c>
       <c r="Z4" s="6">
-        <v>0</v>
+        <v>0.056410256410256411</v>
       </c>
       <c r="AA4" s="8">
-        <v>5.9999255605381165</v>
+        <v>7.7833333774834434</v>
       </c>
       <c r="AB4" s="8">
-        <v>2.1694278106508875</v>
+        <v>2.5748986086956522</v>
       </c>
       <c r="AC4" s="8">
-        <v>8.2262710000000006</v>
+        <v>10.570243</v>
       </c>
       <c r="AD4" s="8">
-        <v>15.025241040462427</v>
+        <v>17.400455897435897</v>
       </c>
       <c r="AE4" s="6">
-        <v>0.96531791907514453</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AF4" s="9"/>
       <c r="AG4" s="5">
-        <v>-231.80000000000001</v>
+        <v>-630.79999999999995</v>
       </c>
       <c r="AH4" s="10">
         <v>5</v>
@@ -2051,7 +2051,7 @@
         <v>19519</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>44</v>
@@ -2088,59 +2088,59 @@
         <v>52</v>
       </c>
       <c r="O11" s="5">
-        <v>102220.93999999999</v>
+        <v>122580.37</v>
       </c>
       <c r="P11" s="5">
-        <v>119257.76333333332</v>
+        <v>122580.37</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.20670098230027389</v>
+        <v>0.2403205355804876</v>
       </c>
       <c r="R11" s="7">
-        <v>1363.8333333333335</v>
+        <v>1391</v>
       </c>
       <c r="S11" s="6">
-        <v>0.25026737967914436</v>
+        <v>0.23315602836879434</v>
       </c>
       <c r="T11" s="6">
-        <v>0.28611895664430398</v>
+        <v>0.28888116262008351</v>
       </c>
       <c r="U11" s="6">
-        <v>0.0004139924755143124</v>
+        <v>0.0026574385441975744</v>
       </c>
       <c r="V11" s="6">
-        <v>0.017586724403043055</v>
+        <v>0.017460275246354698</v>
       </c>
       <c r="W11" s="6">
-        <v>0.0012326388311435994</v>
+        <v>0.0013888602228888688</v>
       </c>
       <c r="X11" s="8">
-        <v>21.847973684210526</v>
+        <v>22.317710134128166</v>
       </c>
       <c r="Y11" s="6">
-        <v>0.77132486388384758</v>
+        <v>0.76453055141579729</v>
       </c>
       <c r="Z11" s="6">
-        <v>0.0018148820326678765</v>
+        <v>0.0029806259314456036</v>
       </c>
       <c r="AA11" s="8">
-        <v>6.3175139351446106</v>
+        <v>6.6416605592347313</v>
       </c>
       <c r="AB11" s="8">
-        <v>3.5538533944954129</v>
+        <v>3.555103167420814</v>
       </c>
       <c r="AC11" s="8">
-        <v>10.201034</v>
+        <v>10.593809</v>
       </c>
       <c r="AD11" s="8">
-        <v>17.067090199637025</v>
+        <v>17.45481877794337</v>
       </c>
       <c r="AE11" s="6">
-        <v>0.91107078039927403</v>
+        <v>0.89716840536512665</v>
       </c>
       <c r="AF11" s="9"/>
       <c r="AG11" s="5">
-        <v>-2876.8000000000002</v>
+        <v>-3211.3000000000002</v>
       </c>
       <c r="AH11" s="10">
         <v>5</v>
@@ -2261,7 +2261,7 @@
         <v>4.4288096428571428</v>
       </c>
       <c r="AC12" s="8">
-        <v>7.2188330000000001</v>
+        <v>10.216412</v>
       </c>
       <c r="AD12" s="8">
         <v>16.157381071428574</v>
@@ -2313,7 +2313,7 @@
         <v>19560</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2350,55 +2350,55 @@
         <v>52</v>
       </c>
       <c r="O13" s="5">
-        <v>63890.889999999999</v>
+        <v>77302.589999999997</v>
       </c>
       <c r="P13" s="5">
-        <v>74539.371666666659</v>
+        <v>77302.589999999997</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.059897838106800494</v>
+        <v>0.099188874135573091</v>
       </c>
       <c r="R13" s="7">
-        <v>750.16666666666674</v>
+        <v>811</v>
       </c>
       <c r="S13" s="6">
-        <v>-0.041728763040238315</v>
+        <v>-0.021712907117008462</v>
       </c>
       <c r="T13" s="6">
-        <v>0.26710731999507281</v>
+        <v>0.29498196890945055</v>
       </c>
       <c r="U13" s="6">
-        <v>-0.021195128131725822</v>
+        <v>0.0061251531158270384</v>
       </c>
       <c r="V13" s="6">
-        <v>0.044874637057020182</v>
+        <v>0.043009348069708922</v>
       </c>
       <c r="W13" s="6">
-        <v>0.019984077542197332</v>
+        <v>0.019008211755906237</v>
       </c>
       <c r="X13" s="8">
-        <v>22.379820860215055</v>
+        <v>22.913705583756347</v>
       </c>
       <c r="Y13" s="6">
-        <v>0.81505376344086022</v>
+        <v>0.85448392554991537</v>
       </c>
       <c r="Z13" s="6">
-        <v>0.1010752688172043</v>
+        <v>0.093062605752961089</v>
       </c>
       <c r="AA13" s="8">
-        <v>10.524129588607595</v>
+        <v>11.248996110414053</v>
       </c>
       <c r="AB13" s="8">
-        <v>1.5267637566137566</v>
+        <v>1.5624670634920634</v>
       </c>
       <c r="AC13" s="8">
-        <v>12.787940000000001</v>
+        <v>13.666278999999999</v>
       </c>
       <c r="AD13" s="8">
-        <v>17.765985376344084</v>
+        <v>18.564241116751269</v>
       </c>
       <c r="AE13" s="6">
-        <v>0.8086021505376344</v>
+        <v>0.79018612521150589</v>
       </c>
       <c r="AF13" s="9"/>
       <c r="AG13" s="5">
@@ -2753,7 +2753,7 @@
         <v>4.2752039024390243</v>
       </c>
       <c r="AC16" s="8">
-        <v>8.7310890000000008</v>
+        <v>9.4245490000000007</v>
       </c>
       <c r="AD16" s="8">
         <v>16.192592270531399</v>
@@ -2884,7 +2884,7 @@
         <v>2.4479545454545453</v>
       </c>
       <c r="AC17" s="8">
-        <v>4.6310140000000004</v>
+        <v>5.4149219999999998</v>
       </c>
       <c r="AD17" s="8">
         <v>12.283183333333334</v>
@@ -3233,13 +3233,13 @@
         <v>52</v>
       </c>
       <c r="O20" s="5">
-        <v>38956.649999999994</v>
+        <v>38956.650000000001</v>
       </c>
       <c r="P20" s="5">
-        <v>38956.649999999987</v>
+        <v>38956.650000000001</v>
       </c>
       <c r="Q20" s="6">
-        <v>0.36999330066307579</v>
+        <v>0.36999330066307601</v>
       </c>
       <c r="R20" s="7">
         <v>442</v>
